--- a/sheets/대금율보/검수/산조합주 잦은모리.xlsx
+++ b/sheets/대금율보/검수/산조합주 잦은모리.xlsx
@@ -12207,32 +12207,32 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="10.71" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="10.71" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="10.71" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="10.71" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="9" customWidth="1"/>
+    <col min="10" max="10" width="10.71" customWidth="1"/>
     <col min="11" max="11" width="6" customWidth="1"/>
-    <col min="12" max="12" width="9" customWidth="1"/>
+    <col min="12" max="12" width="10.71" customWidth="1"/>
     <col min="13" max="13" width="6" customWidth="1"/>
-    <col min="14" max="14" width="9" customWidth="1"/>
+    <col min="14" max="14" width="10.71" customWidth="1"/>
     <col min="15" max="15" width="6" customWidth="1"/>
-    <col min="16" max="16" width="9" customWidth="1"/>
+    <col min="16" max="16" width="10.71" customWidth="1"/>
     <col min="17" max="17" width="6" customWidth="1"/>
-    <col min="18" max="18" width="9" customWidth="1"/>
+    <col min="18" max="18" width="10.71" customWidth="1"/>
     <col min="19" max="19" width="6" customWidth="1"/>
-    <col min="20" max="20" width="9" customWidth="1"/>
+    <col min="20" max="20" width="10.71" customWidth="1"/>
     <col min="21" max="21" width="6" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="6.0" customHeight="true">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="60" customHeight="1">
+    <row r="2" ht="80.0" customHeight="true">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -12259,7 +12259,7 @@
       <c r="T2" s="20"/>
       <c r="U2" s="20"/>
     </row>
-    <row r="3" ht="56" customHeight="1">
+    <row r="3" ht="178.84" customHeight="true">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -12338,7 +12338,7 @@
       </c>
       <c r="U3" s="22"/>
     </row>
-    <row r="4" ht="56" customHeight="1">
+    <row r="4" ht="178.84" customHeight="true">
       <c r="A4" s="0"/>
       <c r="B4" s="21" t="inlineStr">
         <is>
@@ -12419,7 +12419,7 @@
       </c>
       <c r="U4" s="22"/>
     </row>
-    <row r="5" ht="56" customHeight="1">
+    <row r="5" ht="178.84" customHeight="true">
       <c r="A5" s="0"/>
       <c r="B5" s="21" t="inlineStr">
         <is>
@@ -12494,7 +12494,7 @@
       </c>
       <c r="U5" s="22"/>
     </row>
-    <row r="6" ht="56" customHeight="1">
+    <row r="6" ht="178.84" customHeight="true">
       <c r="A6" s="0"/>
       <c r="B6" s="21" t="inlineStr">
         <is>
@@ -12573,7 +12573,7 @@
       </c>
       <c r="U6" s="22"/>
     </row>
-    <row r="7" ht="56" customHeight="1">
+    <row r="7" ht="178.84" customHeight="true">
       <c r="A7" s="0"/>
       <c r="B7" s="21" t="inlineStr">
         <is>
@@ -12654,7 +12654,7 @@
       </c>
       <c r="U7" s="22"/>
     </row>
-    <row r="8" ht="56" customHeight="1">
+    <row r="8" ht="178.84" customHeight="true">
       <c r="A8" s="0"/>
       <c r="B8" s="21" t="inlineStr">
         <is>
@@ -12737,7 +12737,7 @@
       </c>
       <c r="U8" s="24"/>
     </row>
-    <row r="9" ht="56" customHeight="1">
+    <row r="9" ht="178.84" customHeight="true">
       <c r="A9" s="0"/>
       <c r="B9" s="21" t="inlineStr">
         <is>
@@ -12812,7 +12812,7 @@
       </c>
       <c r="U9" s="22"/>
     </row>
-    <row r="10" ht="56" customHeight="1">
+    <row r="10" ht="178.84" customHeight="true">
       <c r="A10" s="0"/>
       <c r="B10" s="21" t="inlineStr">
         <is>
@@ -12890,10 +12890,10 @@
       </c>
       <c r="U10" s="22"/>
     </row>
-    <row r="11">
+    <row r="11" ht="6.0" customHeight="true">
       <c r="A11" s="0"/>
     </row>
-    <row r="12" ht="60" customHeight="1">
+    <row r="12" ht="80.0" customHeight="true">
       <c r="A12" s="0"/>
       <c r="B12" s="20" t="inlineStr">
         <is>
@@ -12920,7 +12920,7 @@
       <c r="T12" s="20"/>
       <c r="U12" s="20"/>
     </row>
-    <row r="13" ht="56" customHeight="1">
+    <row r="13" ht="178.84" customHeight="true">
       <c r="A13" s="0"/>
       <c r="B13" s="21" t="inlineStr">
         <is>
@@ -13003,7 +13003,7 @@
       </c>
       <c r="U13" s="22"/>
     </row>
-    <row r="14" ht="56" customHeight="1">
+    <row r="14" ht="178.84" customHeight="true">
       <c r="A14" s="0"/>
       <c r="B14" s="21" t="inlineStr">
         <is>
@@ -13086,7 +13086,7 @@
       </c>
       <c r="U14" s="22"/>
     </row>
-    <row r="15" ht="56" customHeight="1">
+    <row r="15" ht="178.84" customHeight="true">
       <c r="A15" s="0"/>
       <c r="B15" s="21" t="inlineStr">
         <is>
@@ -13167,7 +13167,7 @@
       </c>
       <c r="U15" s="22"/>
     </row>
-    <row r="16" ht="56" customHeight="1">
+    <row r="16" ht="178.84" customHeight="true">
       <c r="A16" s="0"/>
       <c r="B16" s="21" t="inlineStr">
         <is>
@@ -13244,7 +13244,7 @@
       </c>
       <c r="U16" s="22"/>
     </row>
-    <row r="17" ht="56" customHeight="1">
+    <row r="17" ht="178.84" customHeight="true">
       <c r="A17" s="0"/>
       <c r="B17" s="21" t="inlineStr">
         <is>
@@ -13327,7 +13327,7 @@
       </c>
       <c r="U17" s="22"/>
     </row>
-    <row r="18" ht="56" customHeight="1">
+    <row r="18" ht="178.84" customHeight="true">
       <c r="A18" s="0"/>
       <c r="B18" s="21" t="inlineStr">
         <is>
@@ -13410,7 +13410,7 @@
       </c>
       <c r="U18" s="22"/>
     </row>
-    <row r="19" ht="56" customHeight="1">
+    <row r="19" ht="178.84" customHeight="true">
       <c r="A19" s="0"/>
       <c r="B19" s="21" t="inlineStr">
         <is>
@@ -13491,7 +13491,7 @@
       </c>
       <c r="U19" s="22"/>
     </row>
-    <row r="20" ht="56" customHeight="1">
+    <row r="20" ht="178.84" customHeight="true">
       <c r="A20" s="0"/>
       <c r="B20" s="21" t="inlineStr">
         <is>
@@ -13566,10 +13566,10 @@
       </c>
       <c r="U20" s="22"/>
     </row>
-    <row r="21">
+    <row r="21" ht="6.0" customHeight="true">
       <c r="A21" s="0"/>
     </row>
-    <row r="22" ht="60" customHeight="1">
+    <row r="22" ht="80.0" customHeight="true">
       <c r="A22" s="0"/>
       <c r="B22" s="20" t="inlineStr">
         <is>
@@ -13596,7 +13596,7 @@
       <c r="T22" s="20"/>
       <c r="U22" s="20"/>
     </row>
-    <row r="23" ht="56" customHeight="1">
+    <row r="23" ht="178.84" customHeight="true">
       <c r="A23" s="0"/>
       <c r="B23" s="21" t="inlineStr">
         <is>
@@ -13679,7 +13679,7 @@
       </c>
       <c r="U23" s="22"/>
     </row>
-    <row r="24" ht="56" customHeight="1">
+    <row r="24" ht="178.84" customHeight="true">
       <c r="A24" s="0"/>
       <c r="B24" s="21" t="inlineStr">
         <is>
@@ -13762,7 +13762,7 @@
       </c>
       <c r="U24" s="22"/>
     </row>
-    <row r="25" ht="56" customHeight="1">
+    <row r="25" ht="178.84" customHeight="true">
       <c r="A25" s="0"/>
       <c r="B25" s="21" t="inlineStr">
         <is>
@@ -13843,7 +13843,7 @@
       </c>
       <c r="U25" s="22"/>
     </row>
-    <row r="26" ht="56" customHeight="1">
+    <row r="26" ht="178.84" customHeight="true">
       <c r="A26" s="0"/>
       <c r="B26" s="21" t="inlineStr">
         <is>
@@ -13926,7 +13926,7 @@
       </c>
       <c r="U26" s="22"/>
     </row>
-    <row r="27" ht="56" customHeight="1">
+    <row r="27" ht="178.84" customHeight="true">
       <c r="A27" s="0"/>
       <c r="B27" s="21" t="inlineStr">
         <is>
@@ -14009,7 +14009,7 @@
       </c>
       <c r="U27" s="22"/>
     </row>
-    <row r="28" ht="56" customHeight="1">
+    <row r="28" ht="178.84" customHeight="true">
       <c r="A28" s="0"/>
       <c r="B28" s="21" t="inlineStr">
         <is>
@@ -14092,7 +14092,7 @@
       </c>
       <c r="U28" s="22"/>
     </row>
-    <row r="29" ht="56" customHeight="1">
+    <row r="29" ht="178.84" customHeight="true">
       <c r="A29" s="0"/>
       <c r="B29" s="21" t="inlineStr">
         <is>
@@ -14171,7 +14171,7 @@
       </c>
       <c r="U29" s="22"/>
     </row>
-    <row r="30" ht="56" customHeight="1">
+    <row r="30" ht="178.84" customHeight="true">
       <c r="A30" s="0"/>
       <c r="B30" s="21" t="inlineStr">
         <is>
@@ -14252,10 +14252,10 @@
       </c>
       <c r="U30" s="22"/>
     </row>
-    <row r="31">
+    <row r="31" ht="6.0" customHeight="true">
       <c r="A31" s="0"/>
     </row>
-    <row r="32" ht="60" customHeight="1">
+    <row r="32" ht="80.0" customHeight="true">
       <c r="A32" s="0"/>
       <c r="B32" s="20" t="inlineStr">
         <is>
@@ -14282,7 +14282,7 @@
       <c r="T32" s="20"/>
       <c r="U32" s="20"/>
     </row>
-    <row r="33" ht="56" customHeight="1">
+    <row r="33" ht="178.84" customHeight="true">
       <c r="A33" s="0"/>
       <c r="B33" s="21" t="inlineStr">
         <is>
@@ -14365,7 +14365,7 @@
       </c>
       <c r="U33" s="22"/>
     </row>
-    <row r="34" ht="56" customHeight="1">
+    <row r="34" ht="178.84" customHeight="true">
       <c r="A34" s="0"/>
       <c r="B34" s="21" t="inlineStr">
         <is>
@@ -14448,7 +14448,7 @@
       </c>
       <c r="U34" s="22"/>
     </row>
-    <row r="35" ht="56" customHeight="1">
+    <row r="35" ht="178.84" customHeight="true">
       <c r="A35" s="0"/>
       <c r="B35" s="21" t="inlineStr">
         <is>
@@ -14527,7 +14527,7 @@
       </c>
       <c r="U35" s="22"/>
     </row>
-    <row r="36" ht="56" customHeight="1">
+    <row r="36" ht="178.84" customHeight="true">
       <c r="A36" s="0"/>
       <c r="B36" s="21" t="inlineStr">
         <is>
@@ -14600,7 +14600,7 @@
       </c>
       <c r="U36" s="22"/>
     </row>
-    <row r="37" ht="56" customHeight="1">
+    <row r="37" ht="178.84" customHeight="true">
       <c r="A37" s="0"/>
       <c r="B37" s="21" t="inlineStr">
         <is>
@@ -14683,7 +14683,7 @@
       </c>
       <c r="U37" s="22"/>
     </row>
-    <row r="38" ht="56" customHeight="1">
+    <row r="38" ht="178.84" customHeight="true">
       <c r="A38" s="0"/>
       <c r="B38" s="21" t="inlineStr">
         <is>
@@ -14764,7 +14764,7 @@
       </c>
       <c r="U38" s="22"/>
     </row>
-    <row r="39" ht="56" customHeight="1">
+    <row r="39" ht="178.84" customHeight="true">
       <c r="A39" s="0"/>
       <c r="B39" s="21" t="inlineStr">
         <is>
@@ -14841,7 +14841,7 @@
       </c>
       <c r="U39" s="24"/>
     </row>
-    <row r="40" ht="56" customHeight="1">
+    <row r="40" ht="178.84" customHeight="true">
       <c r="A40" s="0"/>
       <c r="B40" s="21" t="inlineStr">
         <is>
@@ -14916,10 +14916,10 @@
       </c>
       <c r="U40" s="22"/>
     </row>
-    <row r="41">
+    <row r="41" ht="6.0" customHeight="true">
       <c r="A41" s="0"/>
     </row>
-    <row r="42" ht="60" customHeight="1">
+    <row r="42" ht="80.0" customHeight="true">
       <c r="A42" s="0"/>
       <c r="B42" s="20" t="inlineStr">
         <is>
@@ -14946,7 +14946,7 @@
       <c r="T42" s="20"/>
       <c r="U42" s="20"/>
     </row>
-    <row r="43" ht="56" customHeight="1">
+    <row r="43" ht="178.84" customHeight="true">
       <c r="A43" s="0"/>
       <c r="B43" s="21"/>
       <c r="C43" s="22"/>
@@ -14979,7 +14979,7 @@
       </c>
       <c r="U43" s="22"/>
     </row>
-    <row r="44" ht="56" customHeight="1">
+    <row r="44" ht="178.84" customHeight="true">
       <c r="A44" s="0"/>
       <c r="B44" s="21"/>
       <c r="C44" s="22"/>
@@ -15014,7 +15014,7 @@
       </c>
       <c r="U44" s="22"/>
     </row>
-    <row r="45" ht="56" customHeight="1">
+    <row r="45" ht="178.84" customHeight="true">
       <c r="A45" s="0"/>
       <c r="B45" s="21"/>
       <c r="C45" s="22"/>
@@ -15049,7 +15049,7 @@
       </c>
       <c r="U45" s="22"/>
     </row>
-    <row r="46" ht="56" customHeight="1">
+    <row r="46" ht="178.84" customHeight="true">
       <c r="A46" s="0"/>
       <c r="B46" s="21"/>
       <c r="C46" s="22"/>
@@ -15082,7 +15082,7 @@
       </c>
       <c r="U46" s="22"/>
     </row>
-    <row r="47" ht="56" customHeight="1">
+    <row r="47" ht="178.84" customHeight="true">
       <c r="A47" s="0"/>
       <c r="B47" s="21"/>
       <c r="C47" s="22"/>
@@ -15119,7 +15119,7 @@
       </c>
       <c r="U47" s="22"/>
     </row>
-    <row r="48" ht="56" customHeight="1">
+    <row r="48" ht="178.84" customHeight="true">
       <c r="A48" s="0"/>
       <c r="B48" s="21"/>
       <c r="C48" s="22"/>
@@ -15142,7 +15142,7 @@
       <c r="T48" s="21"/>
       <c r="U48" s="22"/>
     </row>
-    <row r="49" ht="56" customHeight="1">
+    <row r="49" ht="178.84" customHeight="true">
       <c r="A49" s="0"/>
       <c r="B49" s="21"/>
       <c r="C49" s="22"/>
@@ -15169,7 +15169,7 @@
       <c r="T49" s="21"/>
       <c r="U49" s="22"/>
     </row>
-    <row r="50" ht="56" customHeight="1">
+    <row r="50" ht="178.84" customHeight="true">
       <c r="A50" s="0"/>
       <c r="B50" s="21"/>
       <c r="C50" s="22"/>
@@ -15208,7 +15208,7 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" scale="61"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="50"/>
   <rowBreaks count="4" manualBreakCount="4">
     <brk id="10" max="16383" man="1"/>
     <brk id="20" max="16383" man="1"/>
